--- a/backend/PDF_DOC/CBIC/Notifications/Tariff/Tariff Notifications.xlsx
+++ b/backend/PDF_DOC/CBIC/Notifications/Tariff/Tariff Notifications.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1FB244C-B26F-4F26-8A06-3D4BD0AA4F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{011D5FBD-E39E-495B-9996-F1EEEABBFC00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="278">
   <si>
     <t>Tariff Notification : 2024</t>
   </si>
@@ -808,6 +808,54 @@
   </si>
   <si>
     <t>Corrigendum to notification No.45/2025-Customs dated 24.10.2025</t>
+  </si>
+  <si>
+    <t>23/2026-Customs</t>
+  </si>
+  <si>
+    <t>Seeks to amend Notification 13/2026-Customs to extend its validity for 15 days till and inclusive of 15th July 2026.</t>
+  </si>
+  <si>
+    <t>22/2026-Customs</t>
+  </si>
+  <si>
+    <t>Seeks to amend Notification 12/2026-Customs to extend its validity for 15 days till and inclusive of 15th July 2026.</t>
+  </si>
+  <si>
+    <t>27/2026-Customs</t>
+  </si>
+  <si>
+    <t>Seeks to amend Notification No. 25/2002-Customs dated 01.03.2002 so as to merge S. Nos. 69 and 69A relating to specified capital goods for manufacture of Lithium Ion Cell.</t>
+  </si>
+  <si>
+    <t>26/2026-Customs</t>
+  </si>
+  <si>
+    <t>Seeks to amend Notification No. 57/2017-Customs dated 30.06.2017 so as to provide BCD exemption on specified goods used in the manufacture of Inductor Coil Module for wireless charging of cellular mobile phones, subject to specified conditions.</t>
+  </si>
+  <si>
+    <t>25/2026-Customs</t>
+  </si>
+  <si>
+    <t>Seeks to amend Notification No. 45/2025-Customs dated 24.10.2025 so as to provide BCD exemption on specified goods used in the manufacture of display assemblies falling under heading 8524 for automotive, medical or industrial applications, subject to specified conditions.</t>
+  </si>
+  <si>
+    <t>24/2026-Customs</t>
+  </si>
+  <si>
+    <t>Notification to give effect to provisions relating to temporary admission of animals under the India-UK CETA</t>
+  </si>
+  <si>
+    <t>28/2026-Customs</t>
+  </si>
+  <si>
+    <t>Amendment in notification no.08/2016</t>
+  </si>
+  <si>
+    <t>29/2026-Customs</t>
+  </si>
+  <si>
+    <t>Seeks to give effect to the first tranche of tariff concessions under India-UK Comprehensive Economic and Trade Agreement (CETA)</t>
   </si>
 </sst>
 </file>
@@ -839,7 +887,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -849,6 +897,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -865,7 +931,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -881,7 +947,26 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="15" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="15" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1162,12 +1247,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.28515625" customWidth="1"/>
     <col min="2" max="2" width="21.85546875" customWidth="1"/>
-    <col min="3" max="3" width="134" style="3" customWidth="1"/>
+    <col min="3" max="3" width="165.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="26.25" x14ac:dyDescent="0.4">
@@ -1186,245 +1271,338 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+    <row r="5" spans="1:3" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5"/>
+      <c r="B5"/>
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" spans="1:3" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="B6" s="17">
+        <v>46217</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="B7" s="13">
+        <v>46213</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="B8" s="13">
+        <v>46211</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="B9" s="13">
+        <v>46211</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="B10" s="13">
+        <v>46211</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="B11" s="13">
+        <v>46206</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="B12" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="B13" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B14" s="7">
         <v>46185</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C14" s="8" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="7" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+    <row r="15" spans="1:3" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B15" s="7">
         <v>46182</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C15" s="8" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+    <row r="16" spans="1:3" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B16" s="7">
         <v>46182</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C16" s="8" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>257</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B17" s="2">
         <v>46172</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>258</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>249</v>
-      </c>
-      <c r="B10" s="2">
-        <v>46154</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>250</v>
-      </c>
-      <c r="B11" s="2">
-        <v>46154</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="B12" s="5">
-        <v>46154</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>253</v>
-      </c>
-      <c r="B13" s="2">
-        <v>46154</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>247</v>
-      </c>
-      <c r="B14" s="2">
-        <v>46142</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>243</v>
-      </c>
-      <c r="B15" s="2">
-        <v>46113</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>245</v>
-      </c>
-      <c r="B16" s="2">
-        <v>46113</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>235</v>
-      </c>
-      <c r="B17" s="2">
-        <v>46112</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="B18" s="2">
-        <v>46112</v>
+        <v>46154</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="B19" s="2">
-        <v>46112</v>
+        <v>46154</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>241</v>
-      </c>
-      <c r="B20" s="2">
-        <v>46111</v>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B20" s="5">
+        <v>46154</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="B21" s="2">
-        <v>46107</v>
+        <v>46154</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="B22" s="2">
-        <v>46093</v>
+        <v>46142</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="B23" s="2">
-        <v>46054</v>
+        <v>46113</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="B24" s="2">
-        <v>46054</v>
+        <v>46113</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="B25" s="2">
-        <v>46054</v>
+        <v>46112</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>237</v>
+      </c>
+      <c r="B26" s="2">
+        <v>46112</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>239</v>
+      </c>
+      <c r="B27" s="2">
+        <v>46112</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>241</v>
+      </c>
+      <c r="B28" s="2">
+        <v>46111</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>233</v>
+      </c>
+      <c r="B29" s="2">
+        <v>46107</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>231</v>
+      </c>
+      <c r="B30" s="2">
+        <v>46093</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>221</v>
+      </c>
+      <c r="B31" s="2">
+        <v>46054</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>223</v>
+      </c>
+      <c r="B32" s="2">
+        <v>46054</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>225</v>
+      </c>
+      <c r="B33" s="2">
+        <v>46054</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>227</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B34" s="2">
         <v>46054</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C34" s="3" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="35" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>229</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B35" s="2">
         <v>46054</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>230</v>
       </c>
     </row>

--- a/backend/PDF_DOC/CBIC/Notifications/Tariff/Tariff Notifications.xlsx
+++ b/backend/PDF_DOC/CBIC/Notifications/Tariff/Tariff Notifications.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{011D5FBD-E39E-495B-9996-F1EEEABBFC00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E230CF-265D-45B7-A7F0-9BEA1C7A73F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="1" r:id="rId1"/>
@@ -887,7 +887,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -915,6 +915,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -958,13 +964,13 @@
     <xf numFmtId="15" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="15" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1247,7 +1253,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.28515625" customWidth="1"/>
@@ -1255,12 +1261,12 @@
     <col min="3" max="3" width="165.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -1271,23 +1277,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5"/>
-      <c r="B5"/>
-      <c r="C5" s="3"/>
-    </row>
-    <row r="6" spans="1:3" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="15">
         <v>46217</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="16" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D6" s="17"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>274</v>
       </c>
@@ -1297,8 +1299,9 @@
       <c r="C7" s="13" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D7" s="17"/>
+    </row>
+    <row r="8" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>266</v>
       </c>
@@ -1308,8 +1311,9 @@
       <c r="C8" s="12" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="D8" s="18"/>
+    </row>
+    <row r="9" spans="1:4" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>268</v>
       </c>
@@ -1319,8 +1323,9 @@
       <c r="C9" s="12" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="D9" s="18"/>
+    </row>
+    <row r="10" spans="1:4" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>270</v>
       </c>
@@ -1330,8 +1335,9 @@
       <c r="C10" s="12" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D10" s="18"/>
+    </row>
+    <row r="11" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>272</v>
       </c>
@@ -1341,8 +1347,9 @@
       <c r="C11" s="12" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D11" s="18"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>262</v>
       </c>
@@ -1352,8 +1359,9 @@
       <c r="C12" s="11" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D12" s="17"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>264</v>
       </c>
@@ -1363,8 +1371,9 @@
       <c r="C13" s="11" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D13" s="17"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>261</v>
       </c>
@@ -1375,7 +1384,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>259</v>
       </c>
@@ -1386,7 +1395,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="16" spans="1:3" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>255</v>
       </c>
@@ -1540,7 +1549,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>231</v>
       </c>
@@ -1551,7 +1560,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>221</v>
       </c>
@@ -1781,7 +1790,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>129</v>
       </c>
@@ -1858,7 +1867,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>142</v>
       </c>
@@ -1869,7 +1878,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>143</v>
       </c>
@@ -2560,7 +2569,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>45</v>
       </c>
@@ -2582,7 +2591,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>49</v>
       </c>
@@ -2593,7 +2602,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>51</v>
       </c>
@@ -2604,7 +2613,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>53</v>
       </c>
@@ -2615,7 +2624,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>55</v>
       </c>
@@ -2626,7 +2635,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>57</v>
       </c>

--- a/backend/PDF_DOC/CBIC/Notifications/Tariff/Tariff Notifications.xlsx
+++ b/backend/PDF_DOC/CBIC/Notifications/Tariff/Tariff Notifications.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E230CF-265D-45B7-A7F0-9BEA1C7A73F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{817177D1-09F8-4C2A-B4D0-A1174F73FFB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="280">
   <si>
     <t>Tariff Notification : 2024</t>
   </si>
@@ -856,6 +856,12 @@
   </si>
   <si>
     <t>Seeks to give effect to the first tranche of tariff concessions under India-UK Comprehensive Economic and Trade Agreement (CETA)</t>
+  </si>
+  <si>
+    <t>30/2026-Customs</t>
+  </si>
+  <si>
+    <t>Seeks to exempt 10 lakh MT of raw sugar falling under tariff heading 1701 from the whole of the customs duty leviable thereon under the First Schedule to the Customs Tariff Act, 1975, up to 31st October, 2026, when imported under the Tariff Rate Quota (TRQ) Scheme (Open General Licence</t>
   </si>
 </sst>
 </file>
@@ -887,7 +893,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -896,31 +902,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1"/>
+        <fgColor rgb="FFCC99FF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -937,7 +919,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -953,32 +935,17 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="15" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="15" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFCC99FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1253,20 +1220,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C36"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.28515625" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
-    <col min="3" max="3" width="165.7109375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="29.33203125" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" customWidth="1"/>
+    <col min="3" max="3" width="165.6640625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="25.8" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -1277,341 +1244,344 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
+    <row r="6" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="B6" s="7">
+        <v>46255</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>276</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B7" s="2">
         <v>46217</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C7" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="D6" s="17"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B8" s="5">
         <v>46213</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C8" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="D7" s="17"/>
-    </row>
-    <row r="8" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+    </row>
+    <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B9" s="5">
         <v>46211</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C9" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="D8" s="18"/>
-    </row>
-    <row r="9" spans="1:4" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+    </row>
+    <row r="10" spans="1:3" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B10" s="5">
         <v>46211</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C10" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="D9" s="18"/>
-    </row>
-    <row r="10" spans="1:4" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+    </row>
+    <row r="11" spans="1:3" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B11" s="5">
         <v>46211</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C11" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="D10" s="18"/>
-    </row>
-    <row r="11" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
+    </row>
+    <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B12" s="5">
         <v>46206</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C12" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="D11" s="18"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>262</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B13" s="2">
         <v>46203</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C13" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="D12" s="17"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>264</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B14" s="2">
         <v>46203</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C14" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="D13" s="17"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>261</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B15" s="2">
         <v>46185</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C15" s="3" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>259</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B16" s="2">
         <v>46182</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C16" s="3" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>255</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B17" s="2">
         <v>46182</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C17" s="3" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>257</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B18" s="2">
         <v>46172</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>249</v>
-      </c>
-      <c r="B18" s="2">
-        <v>46154</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>250</v>
       </c>
       <c r="B19" s="2">
         <v>46154</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>250</v>
+      </c>
+      <c r="B20" s="2">
+        <v>46154</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+    <row r="21" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B21" s="5">
         <v>46154</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>253</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B22" s="2">
         <v>46154</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>247</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B23" s="2">
         <v>46142</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>243</v>
-      </c>
-      <c r="B23" s="2">
-        <v>46113</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>245</v>
       </c>
       <c r="B24" s="2">
         <v>46113</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>245</v>
+      </c>
+      <c r="B25" s="2">
+        <v>46113</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>235</v>
-      </c>
-      <c r="B25" s="2">
-        <v>46112</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>237</v>
       </c>
       <c r="B26" s="2">
         <v>46112</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B27" s="2">
         <v>46112</v>
       </c>
       <c r="C27" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>239</v>
+      </c>
+      <c r="B28" s="2">
+        <v>46112</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>241</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B29" s="2">
         <v>46111</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    <row r="30" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>233</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B30" s="2">
         <v>46107</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>231</v>
       </c>
-      <c r="B30" s="2">
+      <c r="B31" s="2">
         <v>46093</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>221</v>
-      </c>
-      <c r="B31" s="2">
-        <v>46054</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>223</v>
       </c>
       <c r="B32" s="2">
         <v>46054</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B33" s="2">
         <v>46054</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B34" s="2">
         <v>46054</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B35" s="2">
         <v>46054</v>
       </c>
       <c r="C35" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>229</v>
+      </c>
+      <c r="B36" s="2">
+        <v>46054</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>230</v>
       </c>
     </row>
@@ -1624,19 +1594,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E9278BC-9152-4F51-824C-83D141153853}">
   <dimension ref="A1:C65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.28515625" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" customWidth="1"/>
-    <col min="3" max="3" width="142.28515625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="28.33203125" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" customWidth="1"/>
+    <col min="3" max="3" width="142.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="25.8" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -1647,7 +1617,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>105</v>
       </c>
@@ -1658,7 +1628,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>107</v>
       </c>
@@ -1669,7 +1639,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>109</v>
       </c>
@@ -1680,7 +1650,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>111</v>
       </c>
@@ -1691,7 +1661,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>113</v>
       </c>
@@ -1702,7 +1672,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>115</v>
       </c>
@@ -1713,7 +1683,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>117</v>
       </c>
@@ -1724,7 +1694,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>119</v>
       </c>
@@ -1735,7 +1705,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>121</v>
       </c>
@@ -1746,7 +1716,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>123</v>
       </c>
@@ -1757,7 +1727,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>124</v>
       </c>
@@ -1768,7 +1738,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>126</v>
       </c>
@@ -1779,7 +1749,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>127</v>
       </c>
@@ -1790,7 +1760,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>129</v>
       </c>
@@ -1801,7 +1771,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>130</v>
       </c>
@@ -1812,7 +1782,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>132</v>
       </c>
@@ -1823,7 +1793,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>134</v>
       </c>
@@ -1834,7 +1804,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>136</v>
       </c>
@@ -1845,7 +1815,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>138</v>
       </c>
@@ -1856,7 +1826,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>140</v>
       </c>
@@ -1867,7 +1837,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>142</v>
       </c>
@@ -1878,7 +1848,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>143</v>
       </c>
@@ -1889,7 +1859,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>144</v>
       </c>
@@ -1900,7 +1870,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>146</v>
       </c>
@@ -1911,7 +1881,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>148</v>
       </c>
@@ -1922,7 +1892,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>150</v>
       </c>
@@ -1933,7 +1903,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>152</v>
       </c>
@@ -1944,7 +1914,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>154</v>
       </c>
@@ -1955,7 +1925,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>156</v>
       </c>
@@ -1966,7 +1936,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>158</v>
       </c>
@@ -1977,7 +1947,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>160</v>
       </c>
@@ -1988,7 +1958,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>162</v>
       </c>
@@ -1999,7 +1969,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>164</v>
       </c>
@@ -2010,7 +1980,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>166</v>
       </c>
@@ -2021,7 +1991,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>168</v>
       </c>
@@ -2032,7 +2002,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>170</v>
       </c>
@@ -2043,7 +2013,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>172</v>
       </c>
@@ -2054,7 +2024,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>174</v>
       </c>
@@ -2065,7 +2035,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>176</v>
       </c>
@@ -2076,7 +2046,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>178</v>
       </c>
@@ -2087,7 +2057,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>180</v>
       </c>
@@ -2098,7 +2068,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>182</v>
       </c>
@@ -2109,7 +2079,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>184</v>
       </c>
@@ -2120,7 +2090,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>186</v>
       </c>
@@ -2131,7 +2101,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>188</v>
       </c>
@@ -2142,7 +2112,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>190</v>
       </c>
@@ -2153,7 +2123,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>191</v>
       </c>
@@ -2164,7 +2134,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>193</v>
       </c>
@@ -2175,7 +2145,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>195</v>
       </c>
@@ -2186,7 +2156,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>197</v>
       </c>
@@ -2197,7 +2167,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>199</v>
       </c>
@@ -2208,7 +2178,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>201</v>
       </c>
@@ -2219,7 +2189,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>203</v>
       </c>
@@ -2230,7 +2200,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>205</v>
       </c>
@@ -2241,7 +2211,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>207</v>
       </c>
@@ -2252,7 +2222,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>209</v>
       </c>
@@ -2263,7 +2233,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>219</v>
       </c>
@@ -2274,7 +2244,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>212</v>
       </c>
@@ -2285,7 +2255,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>214</v>
       </c>
@@ -2296,7 +2266,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>216</v>
       </c>
@@ -2315,19 +2285,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC3BCC56-3047-4688-A514-1F33469CA6F7}">
   <dimension ref="A1:D55"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.42578125" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" customWidth="1"/>
-    <col min="3" max="3" width="118.28515625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="26.44140625" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" customWidth="1"/>
+    <col min="3" max="3" width="118.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="25.8" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -2338,7 +2308,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -2349,7 +2319,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -2360,7 +2330,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -2371,7 +2341,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -2382,7 +2352,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -2393,7 +2363,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -2404,7 +2374,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -2415,7 +2385,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -2426,7 +2396,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -2437,7 +2407,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -2448,7 +2418,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -2459,7 +2429,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -2470,7 +2440,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>218</v>
       </c>
@@ -2481,7 +2451,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>29</v>
       </c>
@@ -2492,7 +2462,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>31</v>
       </c>
@@ -2503,7 +2473,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -2514,7 +2484,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -2525,7 +2495,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -2536,7 +2506,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -2547,7 +2517,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>41</v>
       </c>
@@ -2558,7 +2528,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>43</v>
       </c>
@@ -2569,7 +2539,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>45</v>
       </c>
@@ -2580,7 +2550,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>47</v>
       </c>
@@ -2591,7 +2561,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>49</v>
       </c>
@@ -2602,7 +2572,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>51</v>
       </c>
@@ -2613,7 +2583,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>53</v>
       </c>
@@ -2624,7 +2594,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>55</v>
       </c>
@@ -2635,7 +2605,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>57</v>
       </c>
@@ -2646,7 +2616,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>59</v>
       </c>
@@ -2657,7 +2627,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>61</v>
       </c>
@@ -2668,7 +2638,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>63</v>
       </c>
@@ -2679,7 +2649,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>65</v>
       </c>
@@ -2693,7 +2663,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>67</v>
       </c>
@@ -2704,7 +2674,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>69</v>
       </c>
@@ -2715,7 +2685,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>71</v>
       </c>
@@ -2726,7 +2696,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>73</v>
       </c>
@@ -2737,7 +2707,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>75</v>
       </c>
@@ -2748,7 +2718,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>77</v>
       </c>
@@ -2759,7 +2729,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>79</v>
       </c>
@@ -2770,7 +2740,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>81</v>
       </c>
@@ -2781,7 +2751,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>83</v>
       </c>
@@ -2792,7 +2762,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>85</v>
       </c>
@@ -2803,7 +2773,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>87</v>
       </c>
@@ -2814,7 +2784,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>89</v>
       </c>
@@ -2825,7 +2795,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>91</v>
       </c>
@@ -2836,7 +2806,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>93</v>
       </c>
@@ -2847,7 +2817,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>95</v>
       </c>
@@ -2858,7 +2828,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>97</v>
       </c>
@@ -2869,7 +2839,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>99</v>
       </c>
@@ -2880,7 +2850,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>101</v>
       </c>
